--- a/Envíos/Operativa_Grupo5_20032026.xlsx
+++ b/Envíos/Operativa_Grupo5_20032026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupoanalistas-my.sharepoint.com/personal/jpuerta_afi_es/Documents/Documentos/Master Quant/Gestión de activos/Trabajo gestión cuantitativa/Trabajo_gestion_cuantitativa/Envíos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{F623CEDB-3327-4B0A-8E02-8998F4DBB3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{217A0971-AD27-496C-A220-493A3B6D7FD5}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{F623CEDB-3327-4B0A-8E02-8998F4DBB3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9179EE2F-1E26-4E01-9B23-1C29CEDE5EA0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Operativa" sheetId="1" r:id="rId1"/>
@@ -114,11 +114,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
     <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;€&quot;;[Red]\-#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.00000_-;\-* #,##0.00000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="170" formatCode="0.0000000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -139,6 +142,13 @@
       <color rgb="FFB5CEA8"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Amasis MT Pro"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -164,20 +174,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -191,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,15 +435,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16.125" customWidth="1"/>
     <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,501 +462,567 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="6">
         <v>74</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="6">
         <v>194.75</v>
       </c>
-      <c r="D2" s="4">
-        <v>9.7375000000000003E-2</v>
-      </c>
-      <c r="E2" s="4">
+      <c r="D2" s="5">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E2" s="6">
         <v>194.847375</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F2" s="8"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="6">
         <v>3</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="6">
         <v>863.5</v>
       </c>
-      <c r="D3" s="4">
-        <v>0.43175000000000002</v>
-      </c>
-      <c r="E3" s="4">
+      <c r="D3" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E3" s="6">
         <v>863.93174999999997</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F3" s="8"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="6">
         <v>1077</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="6">
         <v>40.020000457763601</v>
       </c>
-      <c r="D4" s="4">
-        <v>2.0010000228881799E-2</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="D4" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E4" s="6">
         <v>40.040010457992501</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F4" s="8"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="6">
         <v>112</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="6">
         <v>140.75</v>
       </c>
-      <c r="D5" s="4">
-        <v>7.0374999999999993E-2</v>
-      </c>
-      <c r="E5" s="4">
+      <c r="D5" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E5" s="6">
         <v>140.82037499999899</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F5" s="8"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="3"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="6">
         <v>1</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="6">
         <v>133.5</v>
       </c>
-      <c r="D6" s="4">
-        <v>6.6750000000000004E-2</v>
-      </c>
-      <c r="E6" s="4">
+      <c r="D6" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E6" s="6">
         <v>133.56674999999899</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F6" s="8"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="6">
         <v>24</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="6">
         <v>273.79998779296801</v>
       </c>
-      <c r="D7" s="4">
-        <v>0.136899993896484</v>
-      </c>
-      <c r="E7" s="4">
+      <c r="D7" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E7" s="6">
         <v>273.93688778686499</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F7" s="8"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="6">
         <v>107</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="6">
         <v>153.82000732421801</v>
       </c>
-      <c r="D8" s="4">
-        <v>7.6910003662109303E-2</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="D8" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E8" s="6">
         <v>153.89691732788</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F8" s="8"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <v>380</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="6">
         <v>1656</v>
       </c>
-      <c r="D9" s="4">
-        <v>0.82799999999999996</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="D9" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E9" s="6">
         <v>1656.828</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F9" s="8"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
         <v>26650</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="6">
         <v>23.620000839233398</v>
       </c>
-      <c r="D10" s="4">
-        <v>1.18100004196167E-2</v>
-      </c>
-      <c r="E10" s="4">
+      <c r="D10" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E10" s="6">
         <v>23.631810839652999</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F10" s="8"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>23</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="6">
         <v>9246</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="6">
         <v>68.080001831054602</v>
       </c>
-      <c r="D11" s="4">
-        <v>3.4040000915527301E-2</v>
-      </c>
-      <c r="E11" s="4">
+      <c r="D11" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E11" s="6">
         <v>68.114041831970198</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F11" s="8"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="6">
         <v>-294</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="6">
         <v>65.440002441406193</v>
       </c>
-      <c r="D12" s="4">
-        <v>3.27200012207031E-2</v>
-      </c>
-      <c r="E12" s="4">
+      <c r="D12" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E12" s="6">
         <v>65.407282440185497</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F12" s="8"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>18</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="6">
         <v>-4</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="6">
         <v>584.79998779296795</v>
       </c>
-      <c r="D13" s="4">
-        <v>0.29239999389648402</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E13" s="6">
         <v>584.50758779907198</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F13" s="8"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
         <v>-612</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="6">
         <v>38.384998321533203</v>
       </c>
-      <c r="D14" s="4">
-        <v>1.91924991607666E-2</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E14" s="6">
         <v>38.365805822372401</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F14" s="8"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <v>-472</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="6">
         <v>24.7600002288818</v>
       </c>
-      <c r="D15" s="4">
-        <v>1.23800001144409E-2</v>
-      </c>
-      <c r="E15" s="4">
+      <c r="D15" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E15" s="6">
         <v>24.7476202287673</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F15" s="8"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>7</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="6">
         <v>-36623</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="6">
         <v>17.924999237060501</v>
       </c>
-      <c r="D16" s="4">
-        <v>8.9624996185302692E-3</v>
-      </c>
-      <c r="E16" s="4">
+      <c r="D16" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E16" s="6">
         <v>17.916036737441999</v>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F16" s="8"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="6">
         <v>-429</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="6">
         <v>1503</v>
       </c>
-      <c r="D17" s="4">
-        <v>0.75149999999999995</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="D17" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E17" s="6">
         <v>1502.2484999999999</v>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F17" s="8"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="6">
         <v>-5</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="6">
         <v>1128.19995117187</v>
       </c>
-      <c r="D18" s="4">
-        <v>0.56409997558593705</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E18" s="6">
         <v>1127.6358511962801</v>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F18" s="8"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="6">
         <v>-3871</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="6">
         <v>160.919998168945</v>
       </c>
-      <c r="D19" s="4">
-        <v>8.04599990844726E-2</v>
-      </c>
-      <c r="E19" s="4">
+      <c r="D19" s="6">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E19" s="6">
         <v>160.83953816985999</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F19" s="8"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="6">
         <v>-162.84794965070569</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="6">
         <v>5.032</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="6">
         <v>0</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="6">
         <v>5.032</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
-      <c r="D24" s="5">
-        <v>-819.45088264235096</v>
-      </c>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-    </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="8"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
     </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
     </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
     </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
